--- a/artfynd/A 33529-2021 artfynd.xlsx
+++ b/artfynd/A 33529-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33529-2021 artfynd.xlsx
+++ b/artfynd/A 33529-2021 artfynd.xlsx
@@ -1615,7 +1615,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118302606</v>
+        <v>118302627</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1663,18 +1663,16 @@
           <t>blomknopp</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557146</v>
+        <v>557101</v>
       </c>
       <c r="R10" t="n">
-        <v>6612425</v>
+        <v>6612367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1709,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1718,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1737,7 +1734,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1748,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118302610</v>
+        <v>118302619</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1783,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1802,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557139</v>
+        <v>557116</v>
       </c>
       <c r="R11" t="n">
-        <v>6612438</v>
+        <v>6612384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1839,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>27 bladrosetter, 1 blomstängel i knopp. Bökat av vildsvin intill.</t>
+          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,7 +1864,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1878,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118302601</v>
+        <v>118302606</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,30 +1887,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1921,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557099</v>
+        <v>557146</v>
       </c>
       <c r="R12" t="n">
-        <v>6612415</v>
+        <v>6612425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,6 +1969,11 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1971,12 +1986,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granskog, på granlåga</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1987,7 +1997,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1998,7 +2008,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118302627</v>
+        <v>118302610</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2033,7 +2043,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557101</v>
+        <v>557139</v>
       </c>
       <c r="R13" t="n">
-        <v>6612367</v>
+        <v>6612438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2092,7 +2102,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
+          <t>27 bladrosetter, 1 blomstängel i knopp. Bökat av vildsvin intill.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,7 +2127,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2128,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118302619</v>
+        <v>118302601</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,52 +2150,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557116</v>
+        <v>557099</v>
       </c>
       <c r="R14" t="n">
-        <v>6612384</v>
+        <v>6612415</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2220,23 +2219,24 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog, på granlåga</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 33529-2021 artfynd.xlsx
+++ b/artfynd/A 33529-2021 artfynd.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118302606</v>
+        <v>118302601</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,43 +1887,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1931,10 +1918,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557146</v>
+        <v>557099</v>
       </c>
       <c r="R12" t="n">
-        <v>6612425</v>
+        <v>6612415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1969,11 +1956,6 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1986,7 +1968,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog, på granlåga</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1997,7 +1984,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2127,7 +2114,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2138,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118302601</v>
+        <v>118302606</v>
       </c>
       <c r="B14" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2150,30 +2137,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557099</v>
+        <v>557146</v>
       </c>
       <c r="R14" t="n">
-        <v>6612415</v>
+        <v>6612425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,6 +2219,11 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2231,12 +2236,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granskog, på granlåga</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 33529-2021 artfynd.xlsx
+++ b/artfynd/A 33529-2021 artfynd.xlsx
@@ -1615,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118302627</v>
+        <v>118302601</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,52 +1627,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557101</v>
+        <v>557099</v>
       </c>
       <c r="R10" t="n">
-        <v>6612367</v>
+        <v>6612415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,23 +1696,24 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog, på granlåga</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1734,7 +1724,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1745,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118302619</v>
+        <v>118302606</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,7 +1770,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1793,16 +1783,18 @@
           <t>blomknopp</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557116</v>
+        <v>557146</v>
       </c>
       <c r="R11" t="n">
-        <v>6612384</v>
+        <v>6612425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,7 +1831,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
+          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,6 +1840,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1857,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1875,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118302601</v>
+        <v>118302619</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,41 +1880,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557099</v>
+        <v>557116</v>
       </c>
       <c r="R12" t="n">
-        <v>6612415</v>
+        <v>6612384</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1956,24 +1960,23 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granskog, på granlåga</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,7 +1987,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1998,7 +2001,7 @@
         <v>118302610</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2114,7 +2117,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2125,10 +2128,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118302606</v>
+        <v>118302627</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,7 +2163,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2173,18 +2176,16 @@
           <t>blomknopp</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557146</v>
+        <v>557101</v>
       </c>
       <c r="R14" t="n">
-        <v>6612425</v>
+        <v>6612367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2221,7 +2222,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,7 +2231,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 33529-2021 artfynd.xlsx
+++ b/artfynd/A 33529-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79258870</v>
+        <v>79258861</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556975.9616312158</v>
+        <v>557127</v>
       </c>
       <c r="R2" t="n">
-        <v>6612409.157900623</v>
+        <v>6612379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +743,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79258859</v>
+        <v>79258876</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556988.8874339859</v>
+        <v>557085</v>
       </c>
       <c r="R3" t="n">
-        <v>6612292.050629734</v>
+        <v>6612387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +840,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79258876</v>
+        <v>118302540</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,16 +898,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grytmossen, Vstm</t>
+          <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557085.1926750595</v>
+        <v>557066</v>
       </c>
       <c r="R4" t="n">
-        <v>6612387.058514736</v>
+        <v>6612308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,22 +938,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Plastband Miljöhänsyn Skogsstyrelsen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,55 +957,65 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På liten låga i granskog</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79258866</v>
+        <v>79258859</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556943.0619722726</v>
+        <v>556989</v>
       </c>
       <c r="R5" t="n">
-        <v>6612441.016275901</v>
+        <v>6612292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1058,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,50 +1087,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79258865</v>
+        <v>79258870</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556928.1710017897</v>
+        <v>556976</v>
       </c>
       <c r="R6" t="n">
-        <v>6612421.070947967</v>
+        <v>6612409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1164,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,50 +1193,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79258860</v>
+        <v>118302601</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytmossen, Vstm</t>
+          <t>Grytmossen, söder om, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556984.1476838922</v>
+        <v>557099</v>
       </c>
       <c r="R7" t="n">
-        <v>6612570.06406121</v>
+        <v>6612415</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,22 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,65 +1275,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog, på granlåga</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79258871</v>
+        <v>95025600</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,13 +1358,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557089.9659036441</v>
+        <v>556989</v>
       </c>
       <c r="R8" t="n">
-        <v>6612372.974032364</v>
+        <v>6612340</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,22 +1388,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Unga fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,83 +1411,68 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre granskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95025600</v>
+        <v>79258860</v>
       </c>
       <c r="B9" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556988.6625699265</v>
+        <v>556984</v>
       </c>
       <c r="R9" t="n">
-        <v>6612340.081644494</v>
+        <v>6612570</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,27 +1496,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Unga fruktkroppar.</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,77 +1510,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118302601</v>
+        <v>79258865</v>
       </c>
       <c r="B10" t="n">
-        <v>90511</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grytmossen, söder om, Vstm</t>
+          <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557099</v>
+        <v>556928</v>
       </c>
       <c r="R10" t="n">
-        <v>6612415</v>
+        <v>6612421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,12 +1593,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,99 +1607,63 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Granskog, på granlåga</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Flower Meet 2024</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118302606</v>
+        <v>79258866</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grytmossen, söder om, Vstm</t>
+          <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557146</v>
+        <v>556943</v>
       </c>
       <c r="R11" t="n">
-        <v>6612425</v>
+        <v>6612441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,17 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,92 +1704,63 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Flower Meet 2024</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118302619</v>
+        <v>79258872</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grytmossen, söder om, Vstm</t>
+          <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>557116</v>
       </c>
       <c r="R12" t="n">
-        <v>6612384</v>
+        <v>6612562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,17 +1787,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,40 +1803,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Flower Meet 2024</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118302610</v>
+        <v>79258871</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,31 +1847,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grytmossen, söder om, Vstm</t>
+          <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557139</v>
+        <v>557090</v>
       </c>
       <c r="R13" t="n">
-        <v>6612438</v>
+        <v>6612373</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,17 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>27 bladrosetter, 1 blomstängel i knopp. Bökat av vildsvin intill.</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,42 +1906,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Flower Meet 2024</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118302627</v>
+        <v>79258873</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,31 +1953,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grytmossen, söder om, Vstm</t>
+          <t>Grytmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557101</v>
+        <v>557049</v>
       </c>
       <c r="R14" t="n">
-        <v>6612367</v>
+        <v>6612573</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,17 +1998,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,26 +2012,769 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118231991</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grytmossen nord (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557049</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6612574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>U-Köp-0303</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-07-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-07-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rapportör Jacob Rudhe.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Bengt Stridh</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Bengt Stridh, Jacob Rudhe, Sara Werne</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118302543</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grytmossen, söder om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>557034</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6612309</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 bladrosetter inom ca 1 dm2</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Granskog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118302606</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grytmossen, söder om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557146</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6612425</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>105 bladrosetter, 7 blomstänglar i knopp vid koordinaten inom ca 1 m2. 3 m väserut 6 bladrosetter, 1 blomstängel i knopp och ytterligare några meter västerut vid stort stenblock ytterligare 40 bladrosetter, 2 blomstänglar i knopp. Vid stenblocket var det bökat av vildsvin.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118302610</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grytmossen, söder om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557139</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612438</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>27 bladrosetter, 1 blomstängel i knopp. Bökat av vildsvin intill.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118302619</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grytmossen, söder om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557116</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6612384</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>66 bladrosetter, 2 blomstänglar i knopp</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Flower Meet 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118302627</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grytmossen, söder om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557101</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6612367</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>49 bladrosetter, 1 blomstängel i knopp. Vildsvin hade bökat i marken alldeles nära. Plastband Miljöhänsyn Skogsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sara Werne, Jacob Rudhe, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Flower Meet 2024</t>
         </is>
